--- a/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/03_RedemptionCartPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/03_RedemptionCartPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\04_Redemptions\Redemptions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D2E2F9-994C-4468-AB48-9A3105AF9ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C2CDAB-0355-4A60-AB7D-1C7C884D6FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -342,10 +342,6 @@
 verify_redemptioncart_warningtoastmsg</t>
   </si>
   <si>
-    <t>redemptioncart_clickon_cancelbtn
-verifypagetitle</t>
-  </si>
-  <si>
     <t>Reward Catalogue</t>
   </si>
   <si>
@@ -364,6 +360,11 @@
 redemptioncart_clickon_checkoutbtn
 verifypagetitle
 navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>waitforsnackbardisappear
+redemptioncart_clickon_cancelbtn
+verifypagetitle</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
@@ -1751,17 +1752,17 @@
         <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>5</v>
@@ -1781,16 +1782,16 @@
         <v>39</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>5</v>
